--- a/backend/assets/cfl-uk-manifest-template.xlsx
+++ b/backend/assets/cfl-uk-manifest-template.xlsx
@@ -289,7 +289,7 @@
     <t xml:space="preserve">COTTON SHIRT LADIES SUIT </t>
   </si>
   <si>
-    <t xml:space="preserve">M/S SWITLINE CARGO AND EXPRESS </t>
+    <t xml:space="preserve">M/S SWIFTLINE CARGO AND EXPRESS </t>
   </si>
   <si>
     <t>M/S SWIFTLINE CARGO LTD</t>
